--- a/data/trans_orig/P79A3_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P79A3_2023-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>941</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2428</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6258</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11677</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>67,24%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10948</t>
+          <t>10417</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6618</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11812</t>
+          <t>11358</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>12463</t>
+          <t>11882</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6872</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16482</t>
+          <t>16014</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11812</t>
+          <t>11358</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11812</t>
+          <t>11358</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11812</t>
+          <t>11358</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>18549</t>
+          <t>18140</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18549</t>
+          <t>18140</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18549</t>
+          <t>18140</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>889</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>889</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>61,09%</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4926</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2682</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>6894</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4926</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4926</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4926</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>6894</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>6894</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>6894</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>657</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>657</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>657</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>657</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2132,27 +2132,27 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>708</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>4881</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>91,02%</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2575</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>67,88%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>7231</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>7231</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>7231</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>740</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2510,27 +2510,27 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>738</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>738</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10586</t>
+          <t>9837</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12694</t>
+          <t>13764</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>14207</t>
+          <t>15088</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8047</t>
+          <t>8882</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20853</t>
+          <t>21469</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>50,99%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>18016</t>
+          <t>19702</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>14534</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21204</t>
+          <t>22950</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>6618</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10131</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>27017</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>17988</t>
+          <t>20636</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>30794</t>
+          <t>33223</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>78,9%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>24371</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>24371</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>24371</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
